--- a/healthcare_forms/041_medical_referral_form--healthcare_forms.xlsx
+++ b/healthcare_forms/041_medical_referral_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'dr._smith'}</t>
+          <t>dr._smith</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Dr. Smith'}</t>
+          <t>Dr. Smith</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'dr._johnson'}</t>
+          <t>dr._johnson</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Dr. Johnson'}</t>
+          <t>Dr. Johnson</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'dr._brown'}</t>
+          <t>dr._brown</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Dr. Brown'}</t>
+          <t>Dr. Brown</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'cardiology'}</t>
+          <t>cardiology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Cardiology'}</t>
+          <t>Cardiology</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'dermatology'}</t>
+          <t>dermatology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Dermatology'}</t>
+          <t>Dermatology</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'endocrinology'}</t>
+          <t>endocrinology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Endocrinology'}</t>
+          <t>Endocrinology</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'gastroenterology'}</t>
+          <t>gastroenterology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Gastroenterology'}</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'nephrology'}</t>
+          <t>nephrology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Nephrology'}</t>
+          <t>Nephrology</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'pulmonology'}</t>
+          <t>pulmonology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Pulmonology'}</t>
+          <t>Pulmonology</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'m'}</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'M'}</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'f'}</t>
+          <t>f</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'F'}</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'o'}</t>
+          <t>o</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'O'}</t>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
